--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122279299</v>
+        <v>122279501</v>
       </c>
       <c r="B2" t="n">
-        <v>58245</v>
+        <v>58206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,11 +718,15 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>dvala</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -732,14 +736,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klippan Klingstorp 18:1, Sk</t>
+          <t>Klingstorp 18:2, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399176</v>
+        <v>399267</v>
       </c>
       <c r="R2" t="n">
-        <v>6214736</v>
+        <v>6214651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,22 +770,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122279501</v>
+        <v>122279299</v>
       </c>
       <c r="B3" t="n">
-        <v>58206</v>
+        <v>58245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,21 +829,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -852,15 +856,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>dvala</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -870,14 +870,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klingstorp 18:2, Sk</t>
+          <t>Klippan Klingstorp 18:1, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399267</v>
+        <v>399176</v>
       </c>
       <c r="R3" t="n">
-        <v>6214651</v>
+        <v>6214736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122279501</v>
+        <v>122279299</v>
       </c>
       <c r="B2" t="n">
-        <v>58206</v>
+        <v>58250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,15 +718,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>dvala</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -736,14 +732,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klingstorp 18:2, Sk</t>
+          <t>Klippan Klingstorp 18:1, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399267</v>
+        <v>399176</v>
       </c>
       <c r="R2" t="n">
-        <v>6214651</v>
+        <v>6214736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,22 +766,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122279299</v>
+        <v>122279501</v>
       </c>
       <c r="B3" t="n">
-        <v>58245</v>
+        <v>58211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,21 +825,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -856,11 +852,15 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>dvala</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -870,14 +870,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klippan Klingstorp 18:1, Sk</t>
+          <t>Klingstorp 18:2, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399176</v>
+        <v>399267</v>
       </c>
       <c r="R3" t="n">
-        <v>6214736</v>
+        <v>6214651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122279299</v>
+        <v>122279501</v>
       </c>
       <c r="B2" t="n">
-        <v>58250</v>
+        <v>58211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,11 +718,15 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>dvala</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -732,14 +736,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klippan Klingstorp 18:1, Sk</t>
+          <t>Klingstorp 18:2, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399176</v>
+        <v>399267</v>
       </c>
       <c r="R2" t="n">
-        <v>6214736</v>
+        <v>6214651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,22 +770,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122279501</v>
+        <v>122279299</v>
       </c>
       <c r="B3" t="n">
-        <v>58211</v>
+        <v>58250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,21 +829,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -852,15 +856,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>dvala</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -870,14 +870,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klingstorp 18:2, Sk</t>
+          <t>Klippan Klingstorp 18:1, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399267</v>
+        <v>399176</v>
       </c>
       <c r="R3" t="n">
-        <v>6214651</v>
+        <v>6214736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>208245</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Bufo bufo</t>
@@ -830,11 +825,6 @@
       </c>
       <c r="E3" t="n">
         <v>100141</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Större vattensalamander</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122279501</v>
       </c>
       <c r="B2" t="n">
-        <v>58211</v>
+        <v>58215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>208245</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -811,7 +816,7 @@
         <v>122279299</v>
       </c>
       <c r="B3" t="n">
-        <v>58250</v>
+        <v>58254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,6 +830,11 @@
       </c>
       <c r="E3" t="n">
         <v>100141</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122279501</v>
+        <v>122279299</v>
       </c>
       <c r="B2" t="n">
-        <v>58215</v>
+        <v>58254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,15 +718,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>dvala</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -736,14 +732,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klingstorp 18:2, Sk</t>
+          <t>Klippan Klingstorp 18:1, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399267</v>
+        <v>399176</v>
       </c>
       <c r="R2" t="n">
-        <v>6214651</v>
+        <v>6214736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,22 +766,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122279299</v>
+        <v>122279501</v>
       </c>
       <c r="B3" t="n">
-        <v>58254</v>
+        <v>58215</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,21 +825,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -856,11 +852,15 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>dvala</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -870,14 +870,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klippan Klingstorp 18:1, Sk</t>
+          <t>Klingstorp 18:2, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399176</v>
+        <v>399267</v>
       </c>
       <c r="R3" t="n">
-        <v>6214736</v>
+        <v>6214651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122279299</v>
+        <v>122279501</v>
       </c>
       <c r="B2" t="n">
-        <v>58254</v>
+        <v>58216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,11 +718,15 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
+          <t>dvala</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -732,14 +736,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klippan Klingstorp 18:1, Sk</t>
+          <t>Klingstorp 18:2, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399176</v>
+        <v>399267</v>
       </c>
       <c r="R2" t="n">
-        <v>6214736</v>
+        <v>6214651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,22 +770,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122279501</v>
+        <v>122279299</v>
       </c>
       <c r="B3" t="n">
-        <v>58215</v>
+        <v>58255</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,21 +829,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -852,15 +856,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>dvala</t>
+          <t>på övervintringsplats</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -870,14 +870,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klingstorp 18:2, Sk</t>
+          <t>Klippan Klingstorp 18:1, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399267</v>
+        <v>399176</v>
       </c>
       <c r="R3" t="n">
-        <v>6214651</v>
+        <v>6214736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +904,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37966-2024 artfynd.xlsx
+++ b/artfynd/A 37966-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129709914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129709905</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122279299</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129709889</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122279501</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>